--- a/data/aswasuma day.xlsx
+++ b/data/aswasuma day.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4th year\sem 2\EEX5362 Perfomance Modeling\Miniproject\github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="9">
   <si>
     <t>customerId</t>
   </si>
@@ -52,7 +52,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -65,13 +65,32 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -86,9 +105,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -307,19 +330,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -635,7 +659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -655,7 +679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -675,7 +699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -695,7 +719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -715,7 +739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -735,7 +759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -755,7 +779,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -775,7 +799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -795,7 +819,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -815,7 +839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -835,7 +859,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -855,7 +879,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -875,7 +899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -895,7 +919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -915,27 +939,569 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="31" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="3">
         <v>59.1</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="3">
         <v>34</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="1" t="s">
+      <c r="D31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5">
+        <v>62.9</v>
+      </c>
+      <c r="C32" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="D32" s="5">
+        <v>7</v>
+      </c>
+      <c r="E32" s="5">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="C33">
+        <v>4.5</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>12.5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>66.8</v>
+      </c>
+      <c r="C34">
+        <v>6.3</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>10.3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>69.3</v>
+      </c>
+      <c r="C35">
+        <v>7.8</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+      <c r="E35">
+        <v>12.8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>71.7</v>
+      </c>
+      <c r="C36">
+        <v>5.4</v>
+      </c>
+      <c r="D36">
+        <v>8</v>
+      </c>
+      <c r="E36">
+        <v>13.4</v>
+      </c>
+      <c r="F36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>73.3</v>
+      </c>
+      <c r="C37">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D37">
+        <v>7</v>
+      </c>
+      <c r="E37">
+        <v>15.8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>75.5</v>
+      </c>
+      <c r="C38">
+        <v>9.6</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>13.6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="C39">
+        <v>11.5</v>
+      </c>
+      <c r="D39">
+        <v>7</v>
+      </c>
+      <c r="E39">
+        <v>18.5</v>
+      </c>
+      <c r="F39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="C40">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40">
+        <v>14.2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>81.8</v>
+      </c>
+      <c r="C41">
+        <v>12.3</v>
+      </c>
+      <c r="D41">
+        <v>8</v>
+      </c>
+      <c r="E41">
+        <v>20.3</v>
+      </c>
+      <c r="F41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>83.7</v>
+      </c>
+      <c r="C42">
+        <v>12.4</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>85.7</v>
+      </c>
+      <c r="C43">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43">
+        <v>24.4</v>
+      </c>
+      <c r="F43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>87.3</v>
+      </c>
+      <c r="C44">
+        <v>14.8</v>
+      </c>
+      <c r="D44">
+        <v>8</v>
+      </c>
+      <c r="E44">
+        <v>22.8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>89.2</v>
+      </c>
+      <c r="C45">
+        <v>20.9</v>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="E45">
+        <v>28.9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>90.8</v>
+      </c>
+      <c r="C46">
+        <v>19.3</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>23.3</v>
+      </c>
+      <c r="F46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>93.2</v>
+      </c>
+      <c r="C47">
+        <v>20.9</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>26.9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>95</v>
+      </c>
+      <c r="C48">
+        <v>23.1</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>27.1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>97.2</v>
+      </c>
+      <c r="C49">
+        <v>27.8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>98.8</v>
+      </c>
+      <c r="C50">
+        <v>26.2</v>
+      </c>
+      <c r="D50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>100.7</v>
+      </c>
+      <c r="C51">
+        <v>24.3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>102.8</v>
+      </c>
+      <c r="C52">
+        <v>22.2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>104.8</v>
+      </c>
+      <c r="C53">
+        <v>20.2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>106.5</v>
+      </c>
+      <c r="C54">
+        <v>18.5</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>108.4</v>
+      </c>
+      <c r="C55">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>110.1</v>
+      </c>
+      <c r="C56">
+        <v>14.9</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>111.9</v>
+      </c>
+      <c r="C57">
+        <v>13.1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>114.2</v>
+      </c>
+      <c r="C58">
+        <v>10.8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/aswasuma day.xlsx
+++ b/data/aswasuma day.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="9">
   <si>
     <t>customerId</t>
   </si>
@@ -52,7 +52,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -74,6 +74,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -105,13 +112,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,7 +339,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
@@ -339,7 +348,7 @@
     <col min="6" max="6" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -359,7 +368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -379,7 +388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -399,7 +408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -419,7 +428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -439,7 +448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -459,7 +468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -479,7 +488,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -499,7 +508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -519,7 +528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -539,7 +548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -559,7 +568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -579,7 +588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -599,7 +608,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -619,7 +628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -639,7 +648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -659,7 +668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -679,7 +688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -699,7 +708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -719,7 +728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -739,7 +748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -755,11 +764,11 @@
       <c r="E21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -779,7 +788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -799,7 +808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -819,7 +828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -839,7 +848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -859,7 +868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -879,7 +888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -899,7 +908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -919,7 +928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1481,22 +1490,1002 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58">
+      <c r="A58" s="4">
         <v>57</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="4">
         <v>114.2</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="4">
         <v>10.8</v>
       </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="D58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>116.3</v>
+      </c>
+      <c r="C59">
+        <v>12.2</v>
+      </c>
+      <c r="D59">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>18.2</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6">
+        <v>118.5</v>
+      </c>
+      <c r="C60">
+        <v>10.5</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60">
+        <v>15.5</v>
+      </c>
+      <c r="F60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>120.6</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>7</v>
+      </c>
+      <c r="E61">
+        <v>7</v>
+      </c>
+      <c r="F61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>122.8</v>
+      </c>
+      <c r="C62">
+        <v>8.1</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>12.1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>124.9</v>
+      </c>
+      <c r="C63">
+        <v>6.5</v>
+      </c>
+      <c r="D63">
+        <v>6</v>
+      </c>
+      <c r="E63">
+        <v>12.5</v>
+      </c>
+      <c r="F63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6">
+        <v>127.1</v>
+      </c>
+      <c r="C64" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="D64" s="6">
+        <v>5</v>
+      </c>
+      <c r="E64" s="6">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6">
+        <v>129.30000000000001</v>
+      </c>
+      <c r="C65" s="6">
+        <v>4.8</v>
+      </c>
+      <c r="D65" s="6">
+        <v>8</v>
+      </c>
+      <c r="E65" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6">
+        <v>131.5</v>
+      </c>
+      <c r="C66" s="6">
+        <v>6.1</v>
+      </c>
+      <c r="D66" s="6">
+        <v>5</v>
+      </c>
+      <c r="E66" s="6">
+        <v>11.1</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6">
+        <v>133.6</v>
+      </c>
+      <c r="C67" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="D67" s="6">
+        <v>4</v>
+      </c>
+      <c r="E67" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6">
+        <v>135.80000000000001</v>
+      </c>
+      <c r="C68" s="6">
+        <v>7.2</v>
+      </c>
+      <c r="D68" s="6">
+        <v>6</v>
+      </c>
+      <c r="E68" s="6">
+        <v>13.2</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6">
+        <v>137.9</v>
+      </c>
+      <c r="C69" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="D69" s="6">
+        <v>7</v>
+      </c>
+      <c r="E69" s="6">
+        <v>15.4</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6">
+        <v>140.1</v>
+      </c>
+      <c r="C70" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="D70" s="6">
+        <v>5</v>
+      </c>
+      <c r="E70" s="6">
+        <v>11.8</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>142.30000000000001</v>
+      </c>
+      <c r="C71">
+        <v>5.5</v>
+      </c>
+      <c r="D71">
+        <v>8</v>
+      </c>
+      <c r="E71">
+        <v>13.5</v>
+      </c>
+      <c r="F71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>144.5</v>
+      </c>
+      <c r="C72">
+        <v>4.2</v>
+      </c>
+      <c r="D72">
+        <v>6</v>
+      </c>
+      <c r="E72">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>146.6</v>
+      </c>
+      <c r="C73">
+        <v>3.8</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73">
+        <v>7.8</v>
+      </c>
+      <c r="F73" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="C74">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74">
+        <v>10.1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>151</v>
+      </c>
+      <c r="C75">
+        <v>6.5</v>
+      </c>
+      <c r="D75">
+        <v>7</v>
+      </c>
+      <c r="E75">
+        <v>13.5</v>
+      </c>
+      <c r="F75" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="C76">
+        <v>7.8</v>
+      </c>
+      <c r="D76">
+        <v>6</v>
+      </c>
+      <c r="E76">
+        <v>13.8</v>
+      </c>
+      <c r="F76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>155.4</v>
+      </c>
+      <c r="C77">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77">
+        <v>13.2</v>
+      </c>
+      <c r="F77" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>157.6</v>
+      </c>
+      <c r="C78">
+        <v>6.4</v>
+      </c>
+      <c r="D78">
+        <v>8</v>
+      </c>
+      <c r="E78">
+        <v>14.4</v>
+      </c>
+      <c r="F78" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>159.80000000000001</v>
+      </c>
+      <c r="C79">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D79">
+        <v>4</v>
+      </c>
+      <c r="E79">
+        <v>9.1</v>
+      </c>
+      <c r="F79" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>162</v>
+      </c>
+      <c r="C80">
+        <v>4.5</v>
+      </c>
+      <c r="D80">
+        <v>6</v>
+      </c>
+      <c r="E80">
+        <v>10.5</v>
+      </c>
+      <c r="F80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>164.2</v>
+      </c>
+      <c r="C81">
+        <v>5.8</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81">
+        <v>10.8</v>
+      </c>
+      <c r="F81" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>166.4</v>
+      </c>
+      <c r="C82">
+        <v>6.2</v>
+      </c>
+      <c r="D82">
+        <v>7</v>
+      </c>
+      <c r="E82">
+        <v>13.2</v>
+      </c>
+      <c r="F82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>168.6</v>
+      </c>
+      <c r="C83">
+        <v>5.5</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83">
+        <v>9.5</v>
+      </c>
+      <c r="F83" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>170.8</v>
+      </c>
+      <c r="C84">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+      <c r="E84">
+        <v>9.1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>172.5</v>
+      </c>
+      <c r="C85">
+        <v>2.5</v>
+      </c>
+      <c r="D85" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" t="s">
+        <v>7</v>
+      </c>
+      <c r="F85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>173.8</v>
+      </c>
+      <c r="C86">
+        <v>1.2</v>
+      </c>
+      <c r="D86" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4">
+        <v>174.5</v>
+      </c>
+      <c r="C87" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>175.2</v>
+      </c>
+      <c r="C88">
+        <v>4.5</v>
+      </c>
+      <c r="D88">
+        <v>5</v>
+      </c>
+      <c r="E88">
+        <v>9.5</v>
+      </c>
+      <c r="F88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>178.4</v>
+      </c>
+      <c r="C89">
+        <v>5.2</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>181.5</v>
+      </c>
+      <c r="C90">
+        <v>6</v>
+      </c>
+      <c r="D90">
+        <v>6</v>
+      </c>
+      <c r="E90">
+        <v>12</v>
+      </c>
+      <c r="F90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>184.8</v>
+      </c>
+      <c r="C91">
+        <v>6.8</v>
+      </c>
+      <c r="D91">
+        <v>5</v>
+      </c>
+      <c r="E91">
+        <v>11.8</v>
+      </c>
+      <c r="F91" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>187.9</v>
+      </c>
+      <c r="C92">
+        <v>7.5</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92">
+        <v>11.5</v>
+      </c>
+      <c r="F92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>191.2</v>
+      </c>
+      <c r="C93">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D93">
+        <v>7</v>
+      </c>
+      <c r="E93">
+        <v>15.2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>194.5</v>
+      </c>
+      <c r="C94">
+        <v>9</v>
+      </c>
+      <c r="D94">
+        <v>5</v>
+      </c>
+      <c r="E94">
+        <v>14</v>
+      </c>
+      <c r="F94" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>197.6</v>
+      </c>
+      <c r="C95">
+        <v>10.5</v>
+      </c>
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95">
+        <v>13.5</v>
+      </c>
+      <c r="F95" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>200.8</v>
+      </c>
+      <c r="C96">
+        <v>11.2</v>
+      </c>
+      <c r="D96">
+        <v>6</v>
+      </c>
+      <c r="E96">
+        <v>17.2</v>
+      </c>
+      <c r="F96" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>204.1</v>
+      </c>
+      <c r="C97">
+        <v>12</v>
+      </c>
+      <c r="D97">
+        <v>4</v>
+      </c>
+      <c r="E97">
+        <v>16</v>
+      </c>
+      <c r="F97" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>207.3</v>
+      </c>
+      <c r="C98">
+        <v>14.5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" t="s">
+        <v>7</v>
+      </c>
+      <c r="F98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>210.5</v>
+      </c>
+      <c r="C99">
+        <v>15.2</v>
+      </c>
+      <c r="D99" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" t="s">
+        <v>7</v>
+      </c>
+      <c r="F99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>213.6</v>
+      </c>
+      <c r="C100">
+        <v>16</v>
+      </c>
+      <c r="D100" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>216.8</v>
+      </c>
+      <c r="C101">
+        <v>18.5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" t="s">
+        <v>7</v>
+      </c>
+      <c r="F101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>219.9</v>
+      </c>
+      <c r="C102">
+        <v>20</v>
+      </c>
+      <c r="D102" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" t="s">
+        <v>7</v>
+      </c>
+      <c r="F102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>223.2</v>
+      </c>
+      <c r="C103">
+        <v>22.5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" t="s">
+        <v>7</v>
+      </c>
+      <c r="F103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>226.4</v>
+      </c>
+      <c r="C104">
+        <v>24</v>
+      </c>
+      <c r="D104" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" t="s">
+        <v>7</v>
+      </c>
+      <c r="F104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>229.5</v>
+      </c>
+      <c r="C105">
+        <v>26.5</v>
+      </c>
+      <c r="D105" t="s">
+        <v>7</v>
+      </c>
+      <c r="E105" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>232.1</v>
+      </c>
+      <c r="C106">
+        <v>28</v>
+      </c>
+      <c r="D106" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" t="s">
+        <v>7</v>
+      </c>
+      <c r="F106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>234.8</v>
+      </c>
+      <c r="C107">
+        <v>30.5</v>
+      </c>
+      <c r="D107" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" t="s">
+        <v>7</v>
+      </c>
+      <c r="F107" t="s">
         <v>8</v>
       </c>
     </row>
